--- a/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_children.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_children.xlsx
@@ -15832,7 +15832,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20270427</v>
+        <v>20270430</v>
       </c>
     </row>
   </sheetData>
@@ -54024,8 +54024,8 @@
     <col min="15" max="15" width="15.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="209.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="172.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="207.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="169.71" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="6.71" hidden="0" customWidth="1"/>
   </cols>
@@ -59035,7 +59035,7 @@
     <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="66.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="172.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="169.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="17.71" hidden="0" customWidth="1"/>
     <col min="22" max="22" width="6.71" hidden="0" customWidth="1"/>
   </cols>
@@ -61423,7 +61423,7 @@
     <col min="4" max="4" width="50.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="101.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="225.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="224.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="6.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
@@ -63475,7 +63475,7 @@
     <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="83.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="82.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
   </cols>

--- a/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_children.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_parc_alignedstudies_children.xlsx
@@ -14859,21 +14859,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="116.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -15049,25 +15034,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="196.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="4.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="250.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="69.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="180.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="6.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -15824,9 +15790,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -15851,31 +15814,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="13.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="209.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="16.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="33.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="7.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="51.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="149.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="250.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="15.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="250.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="250.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="17.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -54011,29 +53949,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="6.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="30.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="54.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="34.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="249.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="101.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="150.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="15.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="207.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="169.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -59020,30 +58935,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="91.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="7.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="53.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="22.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="137.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="73.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="7.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="134.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="15.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="66.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="169.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="17.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -60866,23 +60757,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="42.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="5.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="148.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -61421,23 +61295,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="50.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="101.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="224.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="6.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="8.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="108.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="59.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -63465,25 +63322,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="94.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="6.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="82.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -72720,25 +72558,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="49.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="12.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -73098,25 +72917,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="7.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="102.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="250.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="250.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="7.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="6.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
